--- a/Output/Tables/Table_div10_adjusted_malf_card_sex_Femenino.xlsx
+++ b/Output/Tables/Table_div10_adjusted_malf_card_sex_Femenino.xlsx
@@ -424,17 +424,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.96 (0.75, 1.22)</t>
+          <t>0.97 (0.76, 1.25)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.78 (0.17, 3.63)</t>
+          <t>0.90 (0.19, 4.33)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.83 (0.21, 3.29)</t>
+          <t>0.91 (0.22, 3.72)</t>
         </is>
       </c>
     </row>
@@ -451,17 +451,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.01 (0.78, 1.29)</t>
+          <t>1.07 (0.83, 1.36)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.11 (0.22, 5.54)</t>
+          <t>1.40 (0.30, 6.54)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.96 (0.23, 4.03)</t>
+          <t>1.37 (0.33, 5.58)</t>
         </is>
       </c>
     </row>
@@ -478,17 +478,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.26 (0.99, 1.61)</t>
+          <t>1.15 (0.89, 1.49)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.71 (0.81, 17.09)</t>
+          <t>2.58 (0.52, 12.83)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3.99 (0.99, 16.11)</t>
+          <t>2.46 (0.57, 10.61)</t>
         </is>
       </c>
     </row>
@@ -532,17 +532,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.95 (0.85, 1.06)</t>
+          <t>0.96 (0.86, 1.07)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84 (0.23, 3.14)</t>
+          <t>0.93 (0.25, 3.55)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.75 (0.34, 1.65)</t>
+          <t>0.77 (0.34, 1.72)</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.96 (0.85, 1.07)</t>
+          <t>0.97 (0.87, 1.09)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.77 (0.19, 3.06)</t>
+          <t>0.88 (0.23, 3.37)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.72 (0.31, 1.65)</t>
+          <t>0.79 (0.35, 1.81)</t>
         </is>
       </c>
     </row>
@@ -586,17 +586,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.00 (0.89, 1.11)</t>
+          <t>0.96 (0.85, 1.08)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.72 (0.46, 6.38)</t>
+          <t>1.35 (0.34, 5.47)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.06 (0.48, 2.34)</t>
+          <t>0.86 (0.36, 2.05)</t>
         </is>
       </c>
     </row>
@@ -650,17 +650,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.20 (0.88, 1.64)</t>
+          <t>1.13 (0.79, 1.62)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.86 (0.39, 20.86)</t>
+          <t>3.29 (0.31, 35.02)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.83 (0.51, 15.68)</t>
+          <t>2.71 (0.35, 20.71)</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.97 (0.75, 1.25)</t>
+          <t>1.09 (0.84, 1.42)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.85 (0.17, 4.30)</t>
+          <t>1.81 (0.34, 9.56)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.82 (0.19, 3.46)</t>
+          <t>1.70 (0.37, 7.82)</t>
         </is>
       </c>
     </row>
@@ -704,17 +704,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.43 (1.03, 1.97)</t>
+          <t>1.26 (0.86, 1.84)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.43 (1.01, 54.93)</t>
+          <t>6.38 (0.57, 71.19)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>7.78 (1.34, 45.16)</t>
+          <t>5.19 (0.63, 42.85)</t>
         </is>
       </c>
     </row>
@@ -731,17 +731,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.96 (0.85, 1.09)</t>
+          <t>0.95 (0.84, 1.07)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.28 (0.27, 5.97)</t>
+          <t>1.01 (0.21, 4.80)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.82 (0.34, 1.97)</t>
+          <t>0.72 (0.30, 1.72)</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.97 (0.84, 1.11)</t>
+          <t>1.00 (0.88, 1.14)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.61 (0.14, 2.66)</t>
+          <t>0.85 (0.21, 3.40)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.73 (0.29, 1.84)</t>
+          <t>0.89 (0.37, 2.16)</t>
         </is>
       </c>
     </row>
@@ -785,17 +785,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.01 (0.89, 1.14)</t>
+          <t>0.95 (0.83, 1.09)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.17 (0.45, 10.40)</t>
+          <t>1.38 (0.27, 7.06)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.12 (0.46, 2.75)</t>
+          <t>0.80 (0.31, 2.08)</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.94 (0.61, 1.46)</t>
+          <t>0.80 (0.51, 1.25)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.45 (0.03, 7.53)</t>
+          <t>0.19 (0.01, 3.70)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.52 (0.04, 6.30)</t>
+          <t>0.23 (0.02, 3.04)</t>
         </is>
       </c>
     </row>
@@ -876,17 +876,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.18 (0.86, 1.64)</t>
+          <t>1.06 (0.72, 1.55)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.34 (0.28, 19.28)</t>
+          <t>1.89 (0.14, 24.65)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.40 (0.39, 14.88)</t>
+          <t>1.62 (0.18, 14.93)</t>
         </is>
       </c>
     </row>
@@ -903,17 +903,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.93 (0.63, 1.38)</t>
+          <t>0.89 (0.54, 1.45)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.48 (0.04, 6.19)</t>
+          <t>0.40 (0.02, 9.54)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.53 (0.06, 4.89)</t>
+          <t>0.44 (0.03, 7.29)</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.38 (0.93, 2.05)</t>
+          <t>1.16 (0.77, 1.75)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.81 (0.38, 60.89)</t>
+          <t>3.39 (0.23, 49.84)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.49 (0.59, 50.77)</t>
+          <t>2.89 (0.27, 30.78)</t>
         </is>
       </c>
     </row>
@@ -957,17 +957,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.85 (0.73, 0.98)</t>
+          <t>0.85 (0.72, 1.01)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.26 (0.05, 1.37)</t>
+          <t>0.19 (0.03, 1.21)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.29 (0.11, 0.81)</t>
+          <t>0.28 (0.09, 0.87)</t>
         </is>
       </c>
     </row>
@@ -984,17 +984,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.08 (0.92, 1.25)</t>
+          <t>1.05 (0.90, 1.22)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.00 (0.39, 10.12)</t>
+          <t>1.91 (0.35, 10.38)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.49 (0.55, 4.02)</t>
+          <t>1.38 (0.49, 3.87)</t>
         </is>
       </c>
     </row>
@@ -1011,17 +1011,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.89 (0.76, 1.04)</t>
+          <t>0.92 (0.78, 1.08)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.27 (0.05, 1.65)</t>
+          <t>0.29 (0.04, 1.83)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.40 (0.14, 1.18)</t>
+          <t>0.44 (0.14, 1.33)</t>
         </is>
       </c>
     </row>
@@ -1038,17 +1038,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.07 (0.93, 1.22)</t>
+          <t>1.05 (0.89, 1.23)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.19 (0.45, 10.70)</t>
+          <t>2.37 (0.42, 13.38)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.41 (0.55, 3.62)</t>
+          <t>1.46 (0.49, 4.33)</t>
         </is>
       </c>
     </row>
